--- a/output/test_cases/MART_SmartSearch_QnA_Log_v1.1_20260817_en.xlsx
+++ b/output/test_cases/MART_SmartSearch_QnA_Log_v1.1_20260817_en.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="6" min="1" max="1"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -620,8 +620,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, SS-SCR-009, component #7 'Actions') was revised to confirm the fixed 'Clear all'/'Apply (n)' action bar at the bottom of the sheet IS a real component (no longer noted as a design gap) — matching the real Figma reference. The 'which source is correct' question is resolved: Figma was correct, the old storyboard (20260816) was out of date. Note: the storyboard text still reads 'Apply (n)' with a count, while the Figma image shows the button as plain 'Apply' with no number — that specific point is still unresolved, see QnA-39.</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="35.05" customHeight="1" s="7">
       <c r="A7" s="11" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -782,8 +790,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, SS-SCR-017) removed the conflicting '2 seconds of silence / 15 seconds max' proposal from the 'items to confirm' list entirely — only the value 'Auto-stops after 6 seconds' remains in the screen description, with no competing value left anywhere in the document. Confirms the official threshold is a fixed 6 seconds.</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="35.05" customHeight="1" s="7">
       <c r="A10" s="11" t="inlineStr">
@@ -818,7 +834,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -832,8 +848,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, SS-SCR-010 note) states: 'The filter must not be retained whenever the customer switches to a new search keyword' — read as: the filter automatically clears when the customer searches a new keyword. Note: the original storyboard sentence is grammatically a bit unclear (it reads like it's listing two options joined by 'or' rather than stating one outcome) — QC has interpreted it the most reasonable way (auto-clear) but recommends BA restate this more explicitly in writing before treating it as fully locked.</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="46.25" customHeight="1" s="7">
       <c r="A11" s="11" t="inlineStr">
@@ -1404,7 +1428,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -1422,8 +1446,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>See QnA-02 — the updated storyboard (v0.1-20260819) now confirms this action bar genuinely exists, matching the Figma reference. The 'PPTX built from an older Figma version' theory is confirmed correct: the PPTX has since been updated to match the latest Figma.</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="91" customHeight="1" s="7">
       <c r="A22" s="11" t="inlineStr">
@@ -2019,37 +2051,2147 @@
       <c r="K32" s="11" t="n"/>
       <c r="L32" s="11" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="7"/>
+    <row r="33" ht="15" customHeight="1" s="7">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Loading Screen — cross-channel performance thresholds (Text/Image/Voice)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-004 (Loading) only documents a shared threshold — 'show Loading only if &gt;300ms' and '&gt;5s -&gt; network error' — which matches NFR-001 (Text, 300ms P95). Does NFR-004 (Image search, 3,000ms P95) and NFR-005 (Voice search, 4,000ms P95 — note: this conflicts with FR-VS-08, which states 6 seconds P95, see below) also apply to this shared Loading component for Image/Voice searches? If the fixed &gt;5s network-error threshold is shared across all 3 channels, could a perfectly normal Voice search (within its valid P95 budget of 4-6s per NFR-005/FR-VS-08) be incorrectly shown as a 'network error'?</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-004 (Storyboard) vs BRD §7 NFR-001/NFR-004/NFR-005 and §5.4 FR-VS-08</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing Loading UI thresholds against BRD §7 cross-channel NFRs)</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Blocks a definitive Pass/Fail for SS-SCR-004-SC1-TC1/TC2 when executed against the Image/Voice channels (current TC data only covers the Text channel); related to QnA-11.</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-004-SC1-TC1, SS-SCR-004-SC1-TC2</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+    </row>
     <row r="34" ht="15" customHeight="1" s="7">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>QnA-31</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Sponsored — data source / eligibility criteria for the Sponsored label</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only describes FR-PR-05 as part of the merged 'FR-PR-01 -&gt; FR-PR-05' range (Ranking &amp; Sorting section), with the single note 'Sponsored: sponsored items are pinned to a fixed slot, must carry a Sponsored label for transparency'. There is no standalone description of FR-PR-05 covering the SOURCE that determines a SKU is Sponsored: which Retail Media auction platform it comes from, which flow tags a SKU as sponsored, or the eligibility criteria. Requesting BA to provide a standalone FR-PR-05 description or point to the relevant Retail Media integration doc.</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>BRD §5.2 (the merged FR-PR-01-&gt;FR-PR-05 range) — related to SS-SCR-005-SC2, SC5</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>QC (tracing the FR-PR-05 requirement back to its source)</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>BA / Retail Media</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Doesn't block the existing label-visibility/position test cases (already tested against observable UI behavior), but blocks writing a backend integration test case that validates the logic for 'which SKU gets picked as Sponsored'.</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC2-TC1, SS-SCR-005-SC2-TC2, SS-SCR-005-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>QnA-32</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Loading/Fallback — FR-GD-01 and FR-GD-03 are merged together</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>The BRD merges FR-GD-01 and FR-GD-03 into a single 'Performance &amp; Fallback' entry covering two distinct concerns: (1) the overall search performance SLA of &lt;300ms P95, and (2) the Graceful Degradation mechanism — automatically falling back to basic keyword search when AI Search fails/times out, with absolutely no technical error shown to the user. It's unclear which ID maps to which requirement. Requesting BA to split this into two separate entries so each can be traced accurately. Also flagging: the current SS-SCR-004 test suite only covers the Loading UI display thresholds (per the storyboard) — there is NO test case yet for the actual Graceful Degradation behavior (does it really fall back to keyword search when AI Search goes down?). This needs to be added once the requirement is split out.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>BRD §5.2 (the 'FR-GD-01, FR-GD-03' row) — all of SS-SCR-004</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing the merged REQ ID against the BRD)</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>The REQ ID column for the entire SS-SCR-004 test suite currently shares one undifferentiated 'FR-GD-01, FR-GD-03' string; there is also a missing test-case group for the Graceful Degradation behavior itself (none exist in this version).</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-004-SC1-TC1, SC1-TC2, SC2-TC1, SC3-TC1</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>QnA-33</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Search Results — background state after clearing the keyword via (X)</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC2 specifies: tapping (X) on the Search Bar clears the input and switches to the Autocomplete Screen. But it doesn't specify the state of the results page BEHIND the Autocomplete layer at that moment: is the previously-applied filter chip (e.g. 'Sugar-free') and the previously-shown product list KEPT (hidden behind, ready to restore if the customer closes Autocomplete without searching a new term), or CLEARED/RESET as soon as (X) is tapped?</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3 (the storyboard does not describe the background state)</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-005-SC3-TC3 cannot be scored Pass/Fail until this is confirmed.</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>View mode (Grid/List) saved to Local Storage — device switch / account switch</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>FR-PR-07 states the view mode is saved to the DEVICE's Local Storage, not server-side per account. Two cases are not covered: (1) When a Member logs in for the first time on Device B (having previously selected List on Device A) — does Device B sync the List preference from the account, or does it always default to Grid based on the device's own local state? (2) When two different accounts log in one after another on the SAME device (Account 1 selects List then logs out, Account 2 logs in) — does Account 2 inherit List (since it's stored per-device) or does each user get their own state?</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1 / SS-SCR-006-SC1 vs BRD FR-PR-07 (only states 'saved to Local Storage', doesn't specify device-scoped vs account-scoped)</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>New test cases SS-SCR-005-SC1-TC3/TC4 and SS-SCR-006-SC1-TC3/TC4 cannot be scored Pass/Fail until this is confirmed.</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC3, SS-SCR-005-SC1-TC4, SS-SCR-006-SC1-TC3, SS-SCR-006-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>QnA-35</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Rating display for a product with no reviews yet (0 reviews)</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>The BRD does not define how to display the rating when a SKU has zero reviews — hide the star area entirely, or show "No reviews yet" text? The minimum requirement already agreed while drafting the test case: must NOT show "0.0 stars (0)" or a NaN/empty value that looks bad, but the specific replacement display has not been confirmed.</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC3 (previously mis-linked to QnA-04 — QnA-04 is actually about debounce/fuzzy-match/confidence thresholds and is unrelated to rating display; split out into this dedicated item for accurate lookup, see the note on QnA-04)</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>QC (found while cross-checking the QnA Ref mismatch between QnA-04 and SS-SCR-006-SC3-TC1)</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-006-SC3-TC1 cannot be scored Pass/Fail against a specific display approach until this is confirmed.</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Auto-Correct Banner — bilingual suggestion (input language + system display language)</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>FR-AC-01 only describes a single suggestion banner in the form 'Did you mean [correct term]?' — it does not describe showing TWO suggestions simultaneously when the customer types in a language different from the system UI language (e.g. UI=VI, customer types in English/Russian): specifically, a suggestion in the language being typed (shown first, prioritized) PLUS an equivalent Vietnamese suggestion (the system's current display language). This bilingual mechanism is also not mentioned in FR-SM-02 (multilingual) or FR-SM-04 (synonyms). Requesting BA to confirm whether this is intended v1 behavior, and if so, to define the exact display format for showing two suggestions at once.</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4 vs BRD FR-AC-01, FR-SM-02, FR-SM-04 (none mention simultaneous bilingual suggestions)</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>QC (test case requested during review round 3)</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>New test cases SS-SCR-003-SC4-TC2/TC3 cannot be scored Pass/Fail against a specific bilingual behavior until this is confirmed.</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC2, SS-SCR-003-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Sort — definition &amp; tie-break rule for each option ('legacy system logic' QC has no visibility into)</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-06 only states 'the remaining 7 options... keep the same sorting logic as the legacy system' without describing that logic. The real Figma reference (Text Search.png) has a short subtitle for each option ('Lượt mua cao nhất' = highest purchase count, 'Được quan tâm nhiều' = most viewed, '% khuyến mãi cao nhất' = highest discount %, 'Sao trung bình cao nhất' = highest average rating, 'Rẻ nhất lên trên' = cheapest first, 'Đắt nhất lên trên' = priciest first, 'Theo thứ tự bảng chữ cái' = alphabetical), but that isn't enough technical detail for QC to write a precise quantitative test case. Specifically need BA/TD to confirm: (1) is 'purchase count' Order Count or Item Quantity (and over what time window)? (2) is 'most viewed' PDP views or search-result impressions, over what window? (3) is 'average rating' a raw average or a review-count-weighted/Bayesian average (to avoid a 1-review 5-star SKU beating a 1000-review SKU with a slightly lower average)? (4) what's the tie-break rule when multiple SKUs share the exact same price under the Price sorts?</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1 vs BRD FR-PR-06 ('keeps the legacy system's logic' — no detail given) and the Text Search.png Figma reference (short subtitles only, not enough technical detail)</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review — cannot verify legacy system logic without documentation)</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>The new test cases SS-SCR-008-SC1-TC3 through TC9 (one per Sort option) cannot be scored against a precise quantitative Pass/Fail until an official definition is provided.</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3, TC4, TC5, TC6, TC7, TC8</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>QnA-38</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Smart Filter — tag generation formula (Information Gain) &amp; display order (FR-SF-03)</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>FR-SF-03 (part of the merged FR-SF-01-&gt;FR-SF-03 range) only states 'AI pulls up to 10 smart filter tags with the highest Information Gain... flat structure, not grouped'. There is no description of: the Information Gain formula, the minimum threshold for a tag to qualify for display, or the chip display order (descending Information Gain? grouped by attribute type?). This applies to both the on-page Smart Filter Chips row (SS-SCR-005-SC9) and the Labels tab inside the detailed Filter sheet (SS-SCR-009, since per FR-SF-04 the Labels tab is 'based on the smart filter list' — the same underlying data source).</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9 / SS-SCR-009-SC3 vs BRD FR-SF-01-&gt;03</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-009-SC3-TC2 cannot be scored against a precise Pass/Fail until the official formula is provided.</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3-TC2</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Filter — count badges: per-tab (present in Figma) vs the total badge on the Filter button (absent in Figma)</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Re-checking the real Figma reference (Text Search.png, brightness-corrected — see QnA-16) revealed: (1) INSIDE the Filter sheet, each tab (Category/Labels/Delivery/Rating/Price) DOES show its own count badge equal to the number of conditions selected within that tab (e.g. the Labels tab with 3 chips selected shows badge='3') — this detail is not mentioned anywhere in the PPTX storyboard or the BRD. (2) The 'Apply' button at the bottom of the sheet does NOT carry a '(n)' count suffix as the storyboard text describes ('Tap Apply (n)'). (3) Most importantly: the 'Filter' button on the results page (SS-SCR-005, outside the sheet) shows NO count badge at all even with 3 filter conditions already applied — this directly contradicts the 'Filter button badge = total applied conditions' assumption currently baked into test case SS-SCR-009-SC1-TC1 and the entire SS-SCR-010 (Filter Applied State) scenario. Requesting BA/UX to confirm whether this Figma reference is the latest version, and whether a total badge on the Filter button actually exists — if not, the whole SS-SCR-010 suite needs to be rewritten around a different display mechanism (e.g. filter chips shown directly instead of a count badge). [Update 19/08/2026: the latest storyboard (v0.1-20260819) STILL reads 'Apply (n)' with a count in the SS-SCR-009 screen description — confirming the conflict with the Figma reference (no count shown) persists even in the newest version of the document; it has not been reconciled.]</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Text Search.png (real Figma) vs the PPTX storyboard + BRD — related to QnA-02/QnA-18 (same image source, additional detail found on a second pass)</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing the badge shown in the real Figma reference against the assumption used throughout the test suite)</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>High impact: could invalidate the entire "total badge" assumption used in SS-SCR-009-SC1-TC1 and SS-SCR-010-SC1-TC1/SC2-TC1/SC3-TC1 (these existing test cases were NOT modified in this update — the risk is only logged here; they need a follow-up review once this is officially confirmed). The new test case SS-SCR-009-SC6-TC3 cannot be scored Pass/Fail until confirmed.</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC3 (new); risk flagged for SS-SCR-009-SC1-TC1, SS-SCR-010-SC1-TC1, SS-SCR-010-SC2-TC1, SS-SCR-010-SC3-TC1 (not modified)</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Data-prep — Smart Search golden test set</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>The "related" dimension in the keyword-variant matrix has no agreed technical definition yet. Three different readings produce three different expected outputs: (1) Co-purchase — items frequently bought together in the same order; (2) Category-sibling — items in the same category/sub-category; (3) Complementary — items that functionally complement each other (e.g. "fresh milk" -&gt; "cereal", "honey"). BA needs to pick one mechanism (or a weighted combination) before data/glossary/related_terms.csv can be curated and test cases generated for this dimension.</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Test Strategy Artifact - Part 1.2, 1.6 (data/glossary/related_terms.csv)</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>QC (Claude, per user request to assess the Smart Search test pipeline, 2026-08-19)</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Blocks curating data/glossary/related_terms.csv (currently only has 1 placeholder example row, not usable) and blocks generating real test cases for the "related" dimension in the golden test set.</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Category — display rule for 'All in [Category name]' &amp; the 'All categories' breadcrumb behavior</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>The real Figma reference (Text Search.png) confirms: when the customer drills into a parent category that has children (e.g. 'Food &amp; Beverage &gt; Milk &amp; Eggs'), the system shows a radio option 'All in "Milk &amp; Eggs"' (pre-selected by default) above the list of child categories — selecting this applies the filter to the ENTIRE 'Milk &amp; Eggs' subtree (not narrowed to any single child category). This confirms exactly what QC described. However, the behavior of the '‹ All categories' breadcrumb link at the start (as opposed to intermediate breadcrumb segments like 'Food &amp; Beverage') is not demonstrated in the static image: does tapping it (a) go straight back to the top-level category list (root) AND simultaneously clear the current Category selection entirely (Category tab badge back to 0), or (b) merely navigate the picker UI back to root WITHOUT clearing the previously confirmed Category selection (badge stays at 1, requiring the customer to pick something else and tap Apply to change it)? Requesting BA/UX to confirm.</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4 vs the real Figma reference (Text Search.png) — the 'All categories' breadcrumb interaction is not demonstrated in the static image</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing against the real Figma reference per the review request)</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-009-SC4-TC3 cannot be scored Pass/Fail until confirmed; SC4-TC2 ('All in X') can already be scored since the Figma reference provides direct evidence of the display mechanism.</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC2, SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>QnA-41</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Price filter — is the percentile based on the original (list) price or the post-discount (final) price?</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only describes '3 automatic price range presets... split by percentile of the result set' without specifying whether the percentile is computed on the ORIGINAL price (list price, before discount) or the POST-DISCOUNT price (what the customer actually pays). This distinction matters: many SKUs in the result set carry a discount badge (e.g. -13%, -11%, per the Figma reference); if the percentile is based on list price, a premium SKU on a deep discount could be misclassified into the 'high price' bucket even though what the customer actually pays falls in the 'low price' bucket — producing a filtering experience that doesn't match the customer's expectation (filtering by the price they pay, not the sticker price).</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2 vs BRD FR-SF-04 (the Price section does not state the pricing basis)</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>BA / Merchandising</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-009-SC2-TC2 cannot be scored against a precise quantitative Pass/Fail until the pricing basis is confirmed.</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Delivery — the BRD lists only a single value, unclear how many delivery types actually exist</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>FR-SF-04 describes the 'Delivery' tab in the detailed Filter sheet with exactly one line, 'Standard delivery', with no list of multiple options like the other tabs (Rating lists a full 5 levels, Category/Labels/Price all have clear cardinality rules). There is no 'select 1' or 'select multiple' note for this group unlike the others. Need BA to confirm: (1) is this really the complete list (only one standard-delivery type exists in v1, making this tab effectively a single on/off checkbox), or are other delivery types missing from the documentation (e.g. Express delivery, Same-day delivery, Scheduled time-slot delivery) that the BA simply forgot to include; (2) if there really is only one value, does the UI actually need a dedicated tab for it, or should it be simplified into a single chip/toggle?</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009 (Delivery tab) vs BRD FR-SF-04 (lists only 'Standard delivery')</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-009-SC9-TC1 cannot be scored against precise details (option count, UI structure) until the complete list is confirmed.</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, SS-SCR-009, component #6) now explicitly confirms: 'Delivery &amp; other groups || Checkbox "Standard delivery"' — confirming this is exactly 1 on/off checkbox, with no other delivery type in v1. Question (1) is answered: yes, this is the complete list. Question (2), about whether the UI structure needs its own dedicated tab, is left to the UX team's discretion and doesn't affect test behavior.</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>QnA-43</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Graceful Degradation — is the SLA threshold relaxed while running in Keyword-search fallback mode?</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>FR-GD-01/NFR-001 sets a 300ms P95 SLA for normal AI search mode; FR-GD-03/NFR-009 states that when AI Search fails, the system automatically degrades (Graceful Degradation) to the basic keyword search algorithm, with no error shown to the customer. However, the BRD doesn't specify: while running in FALLBACK MODE (basic keyword), does the 300ms P95 performance threshold still apply unchanged, or is it relaxed/tightened differently (the keyword algorithm is simpler than AI and could be notably faster, but could also be slower if the legacy keyword-search infrastructure isn't sized for current load)?</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>INT-13-SC2 (Graceful Degradation) vs BRD §7 NFR-001/NFR-009 (does not specify the SLA threshold that applies in fallback mode)</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review while writing the Graceful Degradation test case)</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>The new test case INT-13-SC2-TC2 cannot be scored against a precise quantitative Pass/Fail until the fallback-mode SLA threshold is confirmed.</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Zero Result vs Out-of-stock — where is the trigger boundary when ALL exact-matching SKUs are out of stock?</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>FR-PR-01-&gt;05 defines the Out-of-stock override rule: 'pushed to the bottom of the list (ignoring its score)' — meaning an out-of-stock SKU is STILL shown on the results page (SS-SCR-005), just pushed to the end, NOT excluded from the results. This implies: if a customer's keyword exactly matches 1 out-of-stock SKU but several other SKUs (also matching the keyword) are in stock, the system stays on SS-SCR-005 as normal (the out-of-stock SKU just sits at the bottom) — the Zero Result Page (SS-SCR-012) is NOT triggered, so SS-SCR-012's 'You might like' block never appears for this case either. However, no documentation addresses the EDGE CASE: if ALL SKUs that exactly match the keyword are out of stock (no in-stock exact match remains) — does the system (a) still show SS-SCR-005 with the out-of-stock SKU(s) (even though they can't be purchased right now), or (b) treat this as equivalent to '0 purchasable results' and redirect to the Zero Result Page flow (SS-SCR-012, triggering the Substitute/Cross-sell/Best-seller suggestion block)?</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012 vs BRD FR-PR-01-&gt;05 (the Out-of-stock override only describes the case where other in-stock SKUs exist in the same result set, not the case where everything is out of stock)</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>QC (reviewing the Zero Result trigger boundary per the review request)</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>BA / PO</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-012-SC4-TC2 cannot be scored Pass/Fail until confirmed; SC4-TC1 (other in-stock SKUs exist) can already be scored since the BRD's Out-of-stock override rule is clear for that case.</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC1, SS-SCR-012-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>QnA-45</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Cross-sell (Basket Analysis) — what formula/algorithm determines the suggested add-on products?</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only describes 'Cross-sell (Basket Analysis): mine order history to find items bought together (Corona beer appears in order history -&gt; suggest snacks/peanuts)' — no concrete formula is given. Need BA/TD to confirm: (1) what's the underlying algorithm (association rule mining / market-basket analysis a la Apriori, or a simple co-occurrence count)? (2) is there a minimum threshold (minimum support/confidence) for a product pair to qualify as a suggestion? (3) is the data computed system-wide (aggregated across all customers) or personalized to each customer's own purchase history? (4) what time window of order data is used (all-time or a rolling window, similar to the 3-6 month mechanism used for 'Frequently Purchased' in FR-PS-03)?</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1 vs BRD FR-ZR-02 (Cross-sell — only an illustrative example is given, no formula)</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD / Data</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-012-SC1-TC4 can only verify surface-level behavior (suggestions are plausibly related, not random) — it cannot verify the exact algorithm until an official formula is provided.</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>QnA-46</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Zero Result — 'You might like' defaults to 10 products, but what's the maximum?</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only states 'Apply Lazy Loading, default display of 10 products' for the 'You might like' block — it doesn't specify a maximum cap as the customer keeps scrolling (infinite lazy-loading, or does it stop at a specific threshold, e.g. 30/50 products)? This matters especially for the deepest fallback tier (system-wide Best-sellers), since that list could in theory be very long.</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1 vs BRD FR-ZR-02 (only states a default of 10, no maximum cap mentioned)</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-012-SC1-TC5 cannot be scored against a precise quantitative maximum until confirmed.</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>QnA-47</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Profanity Filter &amp; Trending Search configuration — is manual CMS configuration supported?</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, Slide 26, 'items to confirm' #3) raises two new open questions: (1) can the Profanity Filter used to screen trending keywords (FR-PS-02) be manually configured by an Operator via a CMS, or is it fully automatic against a fixed list? (2) can Trending Search be manually configured (e.g. pinning/hiding a specific keyword), or is it entirely computed by the Trending Score algorithm?</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-001 (Storyboard v0.1-20260819, Slide 26 'items to confirm' #3)</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review after the 19/08/2026 storyboard update)</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>BA / Mart</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>No test case yet covers the manual-configuration capability of either block (Profanity Filter, Trending Search) — needs to be added once decided (if a CMS exists, this needs a separate Admin/CMS-flow test, outside the current customer-facing UI scope).</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>N/A — needs a new TC once specified</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>QnA-48</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Category filter — does it keep the full 5-level hierarchy, or only allow selecting at the leaf level?</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819, Slide 26, 'items to confirm' #4) raises a new question: 'Does the category tree in the filter keep showing the full 5-level hierarchy as it currently does, or does it only display/allow selection at the most specific level (leaf node)?' This question DIRECTLY AFFECTS the SS-SCR-009-SC4 test suite (written based on Figma evidence showing an 'All in [Category name]' option at an INTERMEDIATE level, not only at the leaf) and QnA-40 (the 'All categories' breadcrumb behavior). If the final decision is 'leaf-level selection only,' the intermediate-level 'All in X' option may be removed from the design entirely — needs BA/UX confirmation before treating the current SC4 suite as matching the final design.</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009 (Storyboard v0.1-20260819, Slide 26 'items to confirm' #4) — related to QnA-40, SS-SCR-009-SC4-TC1/TC2/TC3</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review after the 19/08/2026 storyboard update)</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>BA / Mart</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Risk of invalidating the entire assumption behind SS-SCR-009-SC4-TC1 (which confirms an intermediate-level 'All in X' option based on the Figma image) if the final decision is leaf-level-only selection — SC4-TC1 needs a follow-up review once officially confirmed.</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC1, SS-SCR-009-SC4-TC2, SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="11" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>QnA-49</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Gallery — classification labels on the tiles in 'Recent Photos': what's the labeling rule? And are these really photos from the device library?</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>The real Figma reference (Image Search.png, slide 19/SS-SCR-014) shows the 'Recent Photos' grid with 12 tiles, EACH TILE CARRYING A CLASSIFICATION LABEL banner at the bottom (e.g. 'Sữa' [Milk], 'Rau cải' [Vegetables], 'Trứng' [Eggs], 'Thịt' [Meat], 'Táo' [Apple], 'Cá' [Fish], 'Pho mai' [Cheese], 'Sữa chua' [Yogurt], 'Bông cải' [Broccoli], 'Mật ong' [Honey], 'Nước' [Water], 'Dâu tây' [Strawberry]) — this detail is NOT described anywhere in the storyboard's component table (only 5 rows, no mention of labels). Need BA/UX to confirm: (1) how is this classification label generated — does AI auto-detect the image content and tag it, or is it existing file/metadata from the library? (2) MORE IMPORTANTLY: the tiles in the mockup look like GENERIC ILLUSTRATION ICONS per product category, NOT like actual photos from a user's personal photo library — this CONTRADICTS the storyboard's own text description, 'Recent Photos — only pulls the newest photos from the library, sorted descending by time' (implying these should be the customer's real photos, not generic illustration icons). Need confirmation on whether this is just a mockup placeholder (not reflecting the real design) or whether the final design genuinely intends to show an AI-generated classification label over the customer's real photo.</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-014 (Storyboard, Slide 19, component #5 'Photo grid') vs the real Figma reference (Image Search.png) — does not match the text description</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing the real Figma reference Image Search.png against the storyboard description table)</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>No test case yet verifies the classification label on the photos (unclear whether this is a placeholder or the real design); if it is the real design, a dedicated TC needs to be added to check AI-labeling accuracy once decided.</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>N/A — needs a new TC once confirmed</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Recognition-failure screen (image/voice) — where does the header 'Back' button go, and does it duplicate the 'Retry' CTA?</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Both SS-SCR-016 (image not recognized) and SS-SCR-019 (voice not recognized) have a 'Back' button in the header ('Title ... + Back button — the customer always knows which flow they're in') IN ADDITION TO the two main CTAs already defined: 'Retry' (returns to the Camera/Listening screen, keeping the prior mode) and 'Search by keyword' (switches to Pre-search). The storyboard doesn't specify where Back goes: (a) the same destination as 'Retry' (back to the Camera/Listening screen) — making the two buttons redundant, or (b) exits the image/voice-search flow entirely, returning straight to whatever screen opened this flow (usually Pre-search or the previous results page) — different from both main CTAs?</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-016, SS-SCR-019 (Storyboard) — the Back button is only named, its destination is never described</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>The new test case SS-SCR-016-SC1-TC3 cannot be scored Pass/Fail until the Back button's destination is confirmed.</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>QnA-51</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Voice Search — the medium-low confidence suggestion banner (SS-SCR-018-SC1-TC3): is this feature actually in v1 scope?</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>The storyboard (SS-SCR-018, component #7 'Partially misheard') states: 'If confidence is medium-low, show a "Did you mean ...?" banner similar to SS-SCR-003 instead of returning results that might be wrong.' However: (1) the BRD (FR-VS-04/FR-VS-05) does NOT mention this confidence-banner mechanism at all — it only describes navigating straight to results plus allowing manual keyboard edits, with no intermediate verification step of any kind (including a banner). (2) no concrete confidence threshold has been finalized (already logged in QnA-04). Need BA/TD to confirm: is this voice-search suggestion banner genuinely in v1 scope, or just an extra idea noted in the storyboard that was never formally approved in the BRD?</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-018 (Storyboard, component #7) vs BRD FR-VS-04/FR-VS-05 (does not mention this mechanism)</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing the storyboard against the BRD, found while reviewing SS-SCR-018-SC1-TC3)</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-018-SC1-TC3 cannot be scored Pass/Fail until it is confirmed whether this feature is actually in v1 scope.</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>QnA-52</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Admin Ranking Scorecard — 0% test coverage, is there a separate test plan?</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>BRD §3.1 lists 'Admin Ranking Scorecard' as functional area #10 in scope, and BO-05 clearly describes the Merchandising team needing to adjust ranking weights in real time without a code deploy. However, the Storyboard (slide 4, 'Out of scope') itself excludes 'backoffice keyword configuration and Retail Media' from the 19 screens — so the entire Combined Test Suite (which follows the Storyboard) never touches Admin/backoffice at all. Is a separate Admin/backoffice test plan being planned or prepared by another team, or is this a real gap nobody owns yet?</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>BRD §3.1 item #10, BO-05 vs Storyboard slide 4 'Out of scope'</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>QC (reviewing overall scope, BRD vs Storyboard)</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>PO / BA</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>No test case in this suite (UI or Integration) covers the Admin Scorecard functionality — if this is genuinely in go-live scope, it needs an entirely separate test suite.</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>N/A — no TC exists in this suite</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>QnA-53</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>FR-SP-02 and FR-ZR-01 — 2 REQ IDs that do not exist in the BRD but are widely used across the test suite</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>A full-text check of the BRD confirms: (1) FR-SP-02 does NOT appear anywhere in the BRD (the Storyboard assigns this ID to SS-SCR-001 on its own, so all ~17 test cases for the Pre-search screen use an undefined REQ ID); (2) FR-ZR-01 also does NOT exist (the BRD only has FR-ZR-02, used for all of SS-SCR-012). QnA-09 already asked generically about reconciling Storyboard vs BRD REQ IDs, but never named these two specific IDs — requesting BA to confirm: do these two IDs map to an official BRD code, or do they need a new formal definition?</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Full-text comparison against BRD v0.0.3 — related to QnA-09</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>QC (targeted REQ ID review following the test case review)</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Every TC under SS-SCR-001 (SC1–SC9) uses REQ ID 'FR-SP-02', and every TC under SS-SCR-012 (SC1–SC4) uses a REQ ID containing 'FR-ZR-01' — REQ ID traceability confidence is affected until confirmed.</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>All of SS-SCR-001-SC1..SC9 (~17 TCs), all of SS-SCR-012-SC1..SC4 (~11 TCs)</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>QnA-54</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>KPI-04/06/07 — what is the exact measurement formula?</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only states the target thresholds (KPI-04: Search-to-Cart Rate &gt;10%; KPI-06: Query Revision Rate &lt;15-20%; KPI-07: Search Retry Rate &lt;10-15%) without defining the formula: is 'Search-to-Cart' computed per session or per query? What specific event/behavior distinguishes 'Query Revision' (editing the keyword within the same session) from 'Search Retry' (searching again from scratch)? BA/Data Analytics needs to define this clearly before it can be measured post-launch.</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>BRD §2.2 KPI table — only target thresholds, no measurement formula</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>BA / Data Analytics</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Does not directly block Pass/Fail for any TC in the current UI/Integration suite (this is a post-launch measured metric, not a pre-launch testable UI behavior).</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>N/A — falls under Analytics/Instrumentation scope</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>QnA-55</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005 — what is the maximum number of products shown for a single search?</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>No rule found in the BRD/Storyboard for a maximum cap on the main results grid (unlike the 'You might like' block already asked in QnA-46, and 'Frequently Purchased' asked in QnA-58). Does infinite scroll stop at a specific threshold (e.g. 500/1000 products), or keep loading until the entire matching catalogue is exhausted?</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005 — not found in the BRD/Storyboard</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>No test case yet verifies a maximum limit — needs to be added once decided.</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC1, SC1-TC2 (no dedicated TC for a maximum limit yet)</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>QnA-56</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Trending — is a hot keyword with 0 catalogue results filtered out of the Trending block?</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>⚠️ Important finding: the existing test case SS-SCR-001-SC3-TC3 currently ASSUMES ON ITS OWN that 'a 0-result keyword or one that violates the profanity filter must not be shown' — but the BRD (FR-PS-02) ONLY describes filtering through the Profanity Filter, and never mentions filtering out keywords that yield 0 catalogue results. This is an assumption QC added while writing the test case (reasonable from a UX standpoint — avoiding sending customers straight into Zero Result from the Trending block — but never confirmed by BA in writing). Need BA to confirm: does this 0-result filtering rule genuinely exist, or can a trending keyword send a customer straight to the Zero Result Page?</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-02 does not mention 0-result filtering — SS-SCR-001-SC3-TC3 currently assumes it</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>QC (found while reviewing a previously-written test case against the BRD)</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-001-SC3-TC3 is currently testing against a QC assumption with no BRD basis — its Expected Result needs to be re-confirmed (not just a new QnA, the existing TC needs a follow-up review too).</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-001-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>QnA-57</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Trending — when does a search get counted toward Volume?</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Is a search only counted toward the Volume/Velocity score when the customer types a keyword and presses Enter, or does any completion method count (tapping Done on the keyboard, tapping the Search button, or tapping an Autocomplete suggestion)? This directly affects the accuracy of the Trending scoring algorithm (FR-PS-02).</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-02 does not define the search-count event</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>BA / Data</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Does not affect any TC in the current UI suite (this is backend search-counting logic, not observable through the UI).</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>N/A — falls under backend search-counting scope</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>QnA-58</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>'Frequently Purchased' — what is the maximum number of SKUs when scrolling to load more?</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>FR-PS-03 only describes the mechanism: take the Top 10 in-stock SKUs first, then load the next batch of 10 once the customer scrolls past the first batch, 'and so on' — with no stated maximum cap (the same pattern already asked in QnA-46 for the Zero Result 'You might like' block, and QnA-55 for the main results page). Does it stop at a specific count, or keep loading through the customer's entire eligible purchase history?</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-03 — only describes the batch-of-10 mechanism, no maximum stated</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-001-SC8-TC1 currently only tests loading the next batch, it does not verify a specific maximum — needs to be added once confirmed.</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-001-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="11" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>QnA-59</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Autocomplete — the BRD and the Storyboard describe TWO DIFFERENT ranking criteria for the same suggestion list</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>⚠️ Important finding: the BRD (FR-SP-01) describes autocomplete suggestions ranked by "how often the keyword appears in product names" (catalogue text-matching frequency), while the Storyboard (SS-SCR-002, component #2) instead describes "sorted by descending search volume" (historical customer search popularity) — these are TWO COMPLETELY DIFFERENT SIGNALS (catalogue text-matching vs. search-query popularity), not just a wording difference. The existing test case (SS-SCR-002-SC1-TC3) was WRITTEN FOLLOWING THE STORYBOARD'S INTERPRETATION ('popular search keywords', not 'product names matching the string') without ever cross-checking the BRD. On top of that, neither source states a time window for computing 'volume' (all-time or rolling, same open question as other blocks). Need BA/TD to confirm the official criterion.</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-SP-01 vs Storyboard slide 7 (SS-SCR-002) — two different descriptions of the same behavior</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing the BRD against the Storyboard while reviewing an already-written test case)</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-002-SC1-TC3 is currently executing per the Storyboard's interpretation, not yet confirmed as the official source — needs a follow-up review once decided.</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1, SS-SCR-002-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>QnA-60</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Autocomplete — what is the display priority order among exact keyword match / synonym / cross-language / diacritic-normalized / similar product?</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>When a customer types a string, several TYPES of suggestions could match at once (direct catalogue match, synonyms per FR-SM-04, cross-language results per FR-SM-02, diacritic/no-diacritic variants per FR-SM-06, semantically similar products) — no documentation defines the display priority order among these types within the SAME 10-line suggestion list. Specific sub-question: when typing diacritic-free Vietnamese, does the autocomplete list show the suggestion WITH diacritics (normalized) or keep it diacritic-free as typed? (a reasonable inference is with diacritics, per the spirit of FR-SM-06, but this has never been explicitly confirmed for the autocomplete UI specifically).</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-SP-01, FR-SM-02/04/06 — no combined display-priority rule</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>The existing autocomplete test cases (SS-SCR-002-SC1-TC1, TC3, TC4) each test one suggestion type in isolation — none test the case where MULTIPLE suggestion types compete for a position in the same list.</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1, SS-SCR-002-SC1-TC3, SS-SCR-002-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>QnA-61</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>FR-SM-04 Synonym Mapping — who defines/approves the Data Pipeline's automatic run schedule?</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>The BRD states: 'This process is automatically run periodically by the Data Pipeline. The Operator (OP) does not need to configure it manually.' — but never specifies: who decides the run frequency (daily/weekly?), and who checks the quality of the auto-generated synonym pairs (risk: the automated pipeline could produce incorrect mappings that pollute search results with nobody reviewing them).</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-SM-04</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>BA / Data Engineering</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>No UI test case can verify this data-operations/governance question (not observable through the customer-facing interface).</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>N/A — a data operations/governance question</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>QnA-62</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>FR-PR-01→05 — where are the Scorecard weights (Relevance/Purchase Affinity/Margin/Promotion/Trending) configured/stored?</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>Directly related to QnA-52 (Admin Ranking Scorecard outside the Storyboard scope): if the weight-configuration screen (Admin UI) is not among the Storyboard's 19 screens, are the 40%/20%/15%/15%/10% weights currently hardcoded in the codebase, or is there another configuration channel (config file, feature flag, DB) not represented anywhere in this documentation set?</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>BRD §5.2 — related to QnA-52</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>No test case can verify the weight-configuration mechanism (outside customer-facing UI scope).</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>N/A — related to QnA-52</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>QnA-63</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Sponsored — must a sponsored product still be relevant to the searched keyword?</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>QnA-07 already asked about the POSITION of Sponsored placements (fixed slot or auction), but never asked about the ELIGIBILITY CONDITION: must a Sponsored product still fall within the semantically/catalogue-relevant result set for the searched keyword, or can a vendor pay to insert a product that is COMPLETELY UNRELATED into any search result?</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-01→05 — extends QnA-07</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>PO / Retail Media</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>Test cases SS-SCR-005-SC2-TC1/TC2 currently only test the visible label and the out-of-stock rule for Sponsored items, not the relevance-eligibility condition.</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC2-TC1, SS-SCR-005-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>QnA-64</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>FR-PR-01→05 — what is the exact definition of the Margin/Promotion/Trending weight components in the Scorecard?</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>The BRD only states the weight percentages (Margin 15%, Promotion 15%, Trending 10%) without defining: is Margin computed as gross or net profit margin, per SKU or per category? Is Promotion a binary signal (on sale/not) or graded by discount %? Is Trending in this Scorecard context the same Trending Score algorithm as the Trending Search block (FR-PS-02), or an independent signal (e.g. that specific SKU's own recent views/purchases)?</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>BRD §5.2 — only weight percentages, no definitions</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>BA / Merchandising</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-008-SC1-TC3 (AI ranking sanity check) can only verify surface-level behavior (order differs from a simple sort) — it cannot verify each weight component is correct until these are defined.</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>QnA-65</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Does the AI Scorecard (FR-PR-01) apply only to the 'Most Relevant' sort option, or does it also influence the other 7 sort options?</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>FR-PR-01 describes the Scorecard product-scoring algorithm but never states its SCOPE of application. FR-PR-06 (Sorting Options) states the other 7 options (Best Selling, Price, Rating, Name...) 'keep the same sorting logic as the legacy system' — implying the Scorecard applies ONLY to 'Most Relevant' — but needs explicit BA confirmation: do the Out-of-stock override and Sponsored override (which are part of the Scorecard per FR-PR-01→05) also apply simultaneously across all 7 manual sorts (e.g. does an out-of-stock item always get pushed to the bottom even while sorted by Price ascending)?</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-01 vs FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>Test cases SS-SCR-008-SC1-TC3 through TC10 (verifying each sort option) only test the primary ordering of each criterion — they do not clearly test whether the Out-of-stock/Sponsored override applies consistently across all 7 manual sorts.</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3, TC4, TC5, TC6, TC7, TC8, TC9, TC10 — related to QnA-37</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="11" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>QnA-66</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Detailed REQ text for FR-SF-01, FR-SF-02, FR-SF-03 (Smart Filter) — currently merged together, needs to be split apart</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Same pattern already handled in QnA-32 (FR-GD-01/03): the BRD merges FR-SF-01, FR-SF-02, and FR-SF-03 into a single description ('[Smart Filter] AI pulls up to 10 smart filter tags with the highest Information Gain... flat structure, not grouped... the filter shown must always resolve to &gt;=1 product'), without ever separating which content belongs to which of the 3 IDs. Requesting BA to split these apart for more accurate test-case traceability — every Smart-Filter-related TC currently shares the same undifferentiated 'FR-SF-01, FR-SF-04' string.</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>BRD §5.2 'FR-SF-01 -&gt; FR-SF-03'</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>QC (additional review)</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>The REQ ID column for every Smart-Filter-related TC (SS-SCR-005-SC9, SS-SCR-009-SC1/SC3) cannot be broken down by the individual sub-ID.</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC1-TC1, SS-SCR-009-SC3-TC1, SS-SCR-009-SC3-TC2, SS-SCR-005-SC9-TC1, SS-SCR-005-SC9-TC2</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="11" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>QnA-67</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>⚠️ NFR-002 (150ms) conflicts with KPI-02 (&lt;300ms) for the same 'autocomplete response time' metric — and an existing test case cites the wrong number</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>The BRD states two different numbers for the same measurement: NFR-002 = '95% of autocomplete requests return suggestions within 150ms'; KPI-02 = 'Suggestions While Typing, under 0.3 seconds (excluding the 0.3-second debounce window)' = &lt;300ms. Both describe the response time AFTER the debounce has elapsed — a 2x discrepancy, not a rounding difference. MORE SERIOUSLY: the existing test case in this suite (SS-SCR-002-SC1-TC1) currently cites '&lt;=300ms... (P95, NFR-002)' — meaning it is ASSIGNING THE WRONG NUMBER to NFR-002 (the BRD text's actual number is 150ms; 300ms actually matches KPI-02 instead). Need BA to lock in the official number immediately, after which QC will review the existing TC to align it.</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>BRD NFR-002 vs KPI-02 — affects the existing SS-SCR-002-SC1-TC1 (currently citing the wrong REQ ID/number)</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>QC (comparing figures while reviewing the test case)</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-002-SC1-TC1 is currently testing against and citing the WRONG threshold per the BRD text (300ms attributed to NFR-002, when the BRD states 150ms) — this TC needs correcting once BA confirms the official number, though it does NOT currently block Pass/Fail (300ms is still grounded in KPI-02, it is just attributed to the wrong REQ ID).</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n"/>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>Total QnA:</t>
         </is>
       </c>
-      <c r="B34" s="12">
-        <f>COUNTA(A5:A32)</f>
+      <c r="B73" s="12">
+        <f>COUNTA(A5:A71)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Open:</t>
         </is>
       </c>
-      <c r="B35" s="12">
-        <f>COUNTIF(G5:G32,"Open")</f>
+      <c r="B74" s="12">
+        <f>COUNTIF(G5:G71,"Open")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Answered (Resolved):</t>
         </is>
       </c>
-      <c r="B36" s="12">
-        <f>COUNTIF(G5:G32,"Resolved")</f>
+      <c r="B75" s="12">
+        <f>COUNTIF(G5:G71,"Resolved")</f>
         <v/>
       </c>
     </row>
